--- a/powerdist/powerdistUNPLACED.xlsx
+++ b/powerdist/powerdistUNPLACED.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dongg\Documents\Work\ECE49022\powerdist\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nhelushk\Documents\ECE49022\powerdist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2907F886-325B-45D3-B616-D47DA51FA516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87D85D04-126D-4239-8390-E45163E827C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C8A1BAF1-DDE4-4F80-A0F0-37276E3372A7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C8A1BAF1-DDE4-4F80-A0F0-37276E3372A7}"/>
   </bookViews>
   <sheets>
     <sheet name="powerdistDGKY" sheetId="5" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="ExternalData_1" localSheetId="2" hidden="1">'powerdist-all-pos'!$A$1:$G$368</definedName>
-    <definedName name="ExternalData_1" localSheetId="0" hidden="1">powerdistDGKY!$A$1:$D$27</definedName>
+    <definedName name="ExternalData_1" localSheetId="0" hidden="1">powerdistDGKY!$A$1:$D$25</definedName>
     <definedName name="ExternalData_1" localSheetId="1" hidden="1">powerdistUNPLACED!$A$1:$E$49</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1854" uniqueCount="608">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1844" uniqueCount="608">
   <si>
     <t>Designator</t>
   </si>
@@ -1856,9 +1856,6 @@
     <t>DGKY</t>
   </si>
   <si>
-    <t>MQTY</t>
-  </si>
-  <si>
     <t>1MΩ // 1MΩ</t>
   </si>
   <si>
@@ -1884,6 +1881,9 @@
   </si>
   <si>
     <t>GSFC0204</t>
+  </si>
+  <si>
+    <t>MFR</t>
   </si>
 </sst>
 </file>
@@ -2011,8 +2011,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B17E5FB9-A2FA-4FB7-86B3-73A280866DD1}" name="powerdistUNPLACED42" displayName="powerdistUNPLACED42" ref="A1:F27" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F27" xr:uid="{EDE50EC2-F527-4C45-9C10-A892E6CFA439}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B17E5FB9-A2FA-4FB7-86B3-73A280866DD1}" name="powerdistUNPLACED42" displayName="powerdistUNPLACED42" ref="A1:F25" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:F25" xr:uid="{EDE50EC2-F527-4C45-9C10-A892E6CFA439}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{D4FA4818-2C8B-45C1-BBCE-2C88FCDF4D01}" uniqueName="1" name="Designator" queryTableFieldId="1"/>
     <tableColumn id="2" xr3:uid="{F69C4883-C587-44B4-9F28-F875D8913A63}" uniqueName="2" name="Comment" queryTableFieldId="2"/>
@@ -2036,7 +2036,7 @@
     <tableColumn id="5" xr3:uid="{A457F00C-45F6-41B8-A2B2-7BA0514FF857}" uniqueName="5" name="OQTY" queryTableFieldId="6"/>
     <tableColumn id="6" xr3:uid="{B55496FF-3EBF-4EC9-9AE1-5552485E1ED7}" uniqueName="6" name="DGKY" queryTableFieldId="5"/>
     <tableColumn id="8" xr3:uid="{AF398614-9F24-416D-827A-D15BED3DFE69}" uniqueName="8" name="BIDC" queryTableFieldId="8"/>
-    <tableColumn id="9" xr3:uid="{B3B09BBC-3B24-49A1-83A9-597CB57BCE08}" uniqueName="9" name="MQTY" queryTableFieldId="9" dataDxfId="4">
+    <tableColumn id="9" xr3:uid="{B3B09BBC-3B24-49A1-83A9-597CB57BCE08}" uniqueName="9" name="MFR" queryTableFieldId="9" dataDxfId="4">
       <calculatedColumnFormula>SUM(powerdistUNPLACED4[[#This Row],[DGKY]:[BIDC]])</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{5260D42A-CF25-4ED0-A8AF-2BF1BB17B7EC}" uniqueName="7" name="MFRPN" queryTableFieldId="7"/>
@@ -2385,7 +2385,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00309EDC-05AF-4E11-A301-77E80E30ECB5}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.140625" customWidth="1"/>
@@ -2438,30 +2438,30 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
       </c>
       <c r="D3" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -2470,18 +2470,18 @@
         <v>18</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F4" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>
@@ -2490,38 +2490,38 @@
         <v>18</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
         <v>6</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F6" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s">
         <v>6</v>
@@ -2530,18 +2530,18 @@
         <v>29</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
         <v>6</v>
@@ -2550,38 +2550,38 @@
         <v>29</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F8" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C9" t="s">
         <v>6</v>
       </c>
       <c r="D9" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>577</v>
+        <v>603</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C10" t="s">
         <v>6</v>
@@ -2590,7 +2590,7 @@
         <v>34</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F10" t="s">
         <v>604</v>
@@ -2598,10 +2598,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B11" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C11" t="s">
         <v>6</v>
@@ -2618,10 +2618,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B12" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C12" t="s">
         <v>6</v>
@@ -2630,18 +2630,18 @@
         <v>34</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F12" t="s">
-        <v>606</v>
+        <v>584</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C13" t="s">
         <v>6</v>
@@ -2650,18 +2650,18 @@
         <v>34</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B14" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C14" t="s">
         <v>6</v>
@@ -2673,15 +2673,15 @@
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B15" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s">
         <v>6</v>
@@ -2690,249 +2690,209 @@
         <v>34</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F15" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B16" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C16" t="s">
         <v>6</v>
       </c>
       <c r="D16" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="E16">
         <v>3</v>
       </c>
       <c r="F16" t="s">
-        <v>591</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C17" t="s">
-        <v>6</v>
+        <v>76</v>
       </c>
       <c r="D17" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F17" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B18" t="s">
-        <v>76</v>
+        <v>599</v>
       </c>
       <c r="C18" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D18" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F18" t="s">
-        <v>76</v>
+        <v>599</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="B19" t="s">
-        <v>600</v>
+        <v>86</v>
       </c>
       <c r="C19" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D19" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E19">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F19" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C20" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="D20" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="E20">
         <v>2</v>
       </c>
       <c r="F20" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="B21" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="C21" t="s">
         <v>6</v>
       </c>
       <c r="D21" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="E21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F21" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="B22" t="s">
-        <v>90</v>
+        <v>606</v>
       </c>
       <c r="C22" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="D22" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F22" t="s">
-        <v>90</v>
+        <v>606</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>93</v>
+        <v>129</v>
       </c>
       <c r="B23" t="s">
-        <v>94</v>
+        <v>601</v>
       </c>
       <c r="C23" t="s">
         <v>6</v>
       </c>
       <c r="D23" t="s">
-        <v>74</v>
+        <v>131</v>
       </c>
       <c r="E23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F23" t="s">
-        <v>593</v>
+        <v>601</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="B24" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="C24" t="s">
-        <v>110</v>
+        <v>137</v>
       </c>
       <c r="D24" t="s">
-        <v>111</v>
+        <v>138</v>
       </c>
       <c r="E24">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F24" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="B25" t="s">
-        <v>602</v>
+        <v>142</v>
       </c>
       <c r="C25" t="s">
         <v>6</v>
       </c>
       <c r="D25" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="E25">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F25" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>135</v>
-      </c>
-      <c r="B26" t="s">
-        <v>603</v>
-      </c>
-      <c r="C26" t="s">
-        <v>137</v>
-      </c>
-      <c r="D26" t="s">
-        <v>138</v>
-      </c>
-      <c r="E26">
-        <v>4</v>
-      </c>
-      <c r="F26" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>141</v>
-      </c>
-      <c r="B27" t="s">
-        <v>142</v>
-      </c>
-      <c r="C27" t="s">
-        <v>6</v>
-      </c>
-      <c r="D27" t="s">
-        <v>143</v>
-      </c>
-      <c r="E27">
-        <v>7</v>
-      </c>
-      <c r="F27" t="s">
         <v>142</v>
       </c>
     </row>
@@ -2981,7 +2941,7 @@
         <v>595</v>
       </c>
       <c r="H1" t="s">
-        <v>598</v>
+        <v>607</v>
       </c>
       <c r="I1" t="s">
         <v>569</v>
@@ -3064,10 +3024,10 @@
         <v>55</v>
       </c>
       <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
         <v>8</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
       </c>
       <c r="H4">
         <f>SUM(powerdistUNPLACED4[[#This Row],[DGKY]:[BIDC]])</f>
@@ -3344,7 +3304,7 @@
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -3464,7 +3424,7 @@
         <v>3</v>
       </c>
       <c r="I17" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -3554,7 +3514,7 @@
         <v>3</v>
       </c>
       <c r="I20" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -3685,7 +3645,7 @@
         <v>65</v>
       </c>
       <c r="C25" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="D25" t="s">
         <v>34</v>
@@ -3832,7 +3792,7 @@
         <v>78</v>
       </c>
       <c r="B30" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C30" t="s">
         <v>80</v>
@@ -3874,10 +3834,10 @@
         <v>2</v>
       </c>
       <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
         <v>2</v>
-      </c>
-      <c r="G31">
-        <v>0</v>
       </c>
       <c r="H31">
         <f>SUM(powerdistUNPLACED4[[#This Row],[DGKY]:[BIDC]])</f>
@@ -4090,7 +4050,7 @@
         <v>108</v>
       </c>
       <c r="B39" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C39" t="s">
         <v>110</v>
@@ -4112,7 +4072,7 @@
         <v>5</v>
       </c>
       <c r="I39" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -4177,7 +4137,7 @@
         <v>118</v>
       </c>
       <c r="B42" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C42" t="s">
         <v>120</v>
@@ -4297,7 +4257,7 @@
         <v>129</v>
       </c>
       <c r="B46" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C46" t="s">
         <v>6</v>
@@ -4354,7 +4314,7 @@
         <v>135</v>
       </c>
       <c r="B48" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C48" t="s">
         <v>137</v>
